--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2018/GEORGIA_2018.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2018/GEORGIA_2018.xlsx
@@ -2443,7 +2443,7 @@
         <v>24</v>
       </c>
       <c r="D116">
-        <v>0.0009601152138256591</v>
+        <v>0.0009601152138256592</v>
       </c>
     </row>
     <row r="117">
@@ -2958,7 +2958,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Cuatro Cienegas</t>
+          <t>Cuatrocienegas</t>
         </is>
       </c>
       <c r="C145">
@@ -3822,7 +3822,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C193">
@@ -5557,7 +5557,7 @@
         <v>24</v>
       </c>
       <c r="D289">
-        <v>0.0009601152138256591</v>
+        <v>0.0009601152138256592</v>
       </c>
     </row>
     <row r="290">
@@ -6342,7 +6342,7 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C333">
@@ -7267,7 +7267,7 @@
         <v>24</v>
       </c>
       <c r="D384">
-        <v>0.0009601152138256591</v>
+        <v>0.0009601152138256592</v>
       </c>
     </row>
     <row r="385">
@@ -7393,7 +7393,7 @@
         <v>24</v>
       </c>
       <c r="D391">
-        <v>0.0009601152138256591</v>
+        <v>0.0009601152138256592</v>
       </c>
     </row>
     <row r="392">
@@ -12307,7 +12307,7 @@
         <v>244</v>
       </c>
       <c r="D664">
-        <v>0.009761171340560867</v>
+        <v>0.009761171340560868</v>
       </c>
     </row>
     <row r="665">
@@ -13747,7 +13747,7 @@
         <v>24</v>
       </c>
       <c r="D744">
-        <v>0.0009601152138256591</v>
+        <v>0.0009601152138256592</v>
       </c>
     </row>
     <row r="745">
@@ -16206,7 +16206,7 @@
       </c>
       <c r="B881" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C881">
@@ -17052,7 +17052,7 @@
       </c>
       <c r="B928" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C928">
@@ -17070,7 +17070,7 @@
       </c>
       <c r="B929" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 26 -</t>
+          <t>San Pedro Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C929">
@@ -17178,7 +17178,7 @@
       </c>
       <c r="B935" t="inlineStr">
         <is>
-          <t>San Pedro Totolapa</t>
+          <t>San Pedro Totolapam</t>
         </is>
       </c>
       <c r="C935">
@@ -27931,7 +27931,7 @@
         <v>24</v>
       </c>
       <c r="D1532">
-        <v>0.0009601152138256591</v>
+        <v>0.0009601152138256592</v>
       </c>
     </row>
     <row r="1533">
